--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_24-02-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_24-02-2026.xlsx
@@ -304,7 +304,7 @@
     <t>£31.50</t>
   </si>
   <si>
-    <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/xtratherm-thin-r-pitched-roof-insulation-board-24m-x-12m-x-120mm.html (Caused by NameResolutionError("&lt;urllib3.connection.HTTPSConnection object at 0x000002420C6239D0&gt;: Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
+    <t>£39.92</t>
   </si>
   <si>
     <t>£47.50</t>

--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_24-02-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_24-02-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="142">
   <si>
     <t>SKU</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>£40.49</t>
+  </si>
+  <si>
+    <t>Regular price</t>
   </si>
   <si>
     <t>£18.75</t>
@@ -852,37 +855,37 @@
         <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
         <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" t="s">
         <v>56</v>
       </c>
       <c r="H2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K2" t="s">
         <v>56</v>
       </c>
       <c r="L2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -896,37 +899,37 @@
         <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
         <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s">
         <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K3" t="s">
         <v>56</v>
       </c>
       <c r="L3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -940,37 +943,37 @@
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
         <v>48</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K4" t="s">
         <v>56</v>
       </c>
       <c r="L4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -984,37 +987,37 @@
         <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
         <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K5" t="s">
         <v>56</v>
       </c>
       <c r="L5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1028,37 +1031,37 @@
         <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
         <v>50</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K6" t="s">
         <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1072,37 +1075,37 @@
         <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
         <v>51</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K7" t="s">
         <v>56</v>
       </c>
       <c r="L7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1116,37 +1119,37 @@
         <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>52</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K8" t="s">
         <v>56</v>
       </c>
       <c r="L8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1160,37 +1163,37 @@
         <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
         <v>53</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H9" t="s">
         <v>56</v>
       </c>
       <c r="I9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K9" t="s">
         <v>56</v>
       </c>
       <c r="L9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1204,37 +1207,37 @@
         <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E10" t="s">
         <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K10" t="s">
         <v>56</v>
       </c>
       <c r="L10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1248,37 +1251,37 @@
         <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
         <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K11" t="s">
         <v>56</v>
       </c>
       <c r="L11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1298,31 +1301,31 @@
         <v>56</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s">
         <v>56</v>
       </c>
       <c r="I12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K12" t="s">
         <v>56</v>
       </c>
       <c r="L12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1336,37 +1339,37 @@
         <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
         <v>57</v>
       </c>
       <c r="F13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K13" t="s">
         <v>56</v>
       </c>
       <c r="L13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1380,7 +1383,7 @@
         <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
         <v>58</v>
@@ -1398,16 +1401,16 @@
         <v>56</v>
       </c>
       <c r="J14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K14" t="s">
         <v>56</v>
       </c>
       <c r="L14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N14" t="s">
         <v>56</v>
@@ -1424,37 +1427,37 @@
         <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E15" t="s">
         <v>59</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s">
         <v>56</v>
       </c>
       <c r="I15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K15" t="s">
         <v>56</v>
       </c>
       <c r="L15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1468,37 +1471,37 @@
         <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s">
         <v>60</v>
       </c>
       <c r="F16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s">
         <v>56</v>
       </c>
       <c r="I16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K16" t="s">
         <v>56</v>
       </c>
       <c r="L16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1512,37 +1515,37 @@
         <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
         <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K17" t="s">
         <v>56</v>
       </c>
       <c r="L17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_24-02-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_24-02-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="143">
   <si>
     <t>SKU</t>
   </si>
@@ -202,7 +202,7 @@
     <t>£40.49</t>
   </si>
   <si>
-    <t>Regular price</t>
+    <t>£300</t>
   </si>
   <si>
     <t>£18.75</t>
@@ -395,6 +395,9 @@
   </si>
   <si>
     <t>£59.44</t>
+  </si>
+  <si>
+    <t>£49.00</t>
   </si>
   <si>
     <t>£14.54</t>
@@ -885,7 +888,7 @@
         <v>118</v>
       </c>
       <c r="N2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -929,7 +932,7 @@
         <v>118</v>
       </c>
       <c r="N3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -973,7 +976,7 @@
         <v>118</v>
       </c>
       <c r="N4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1017,7 +1020,7 @@
         <v>118</v>
       </c>
       <c r="N5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1061,7 +1064,7 @@
         <v>118</v>
       </c>
       <c r="N6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1105,7 +1108,7 @@
         <v>118</v>
       </c>
       <c r="N7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1149,7 +1152,7 @@
         <v>118</v>
       </c>
       <c r="N8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1193,7 +1196,7 @@
         <v>118</v>
       </c>
       <c r="N9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1237,7 +1240,7 @@
         <v>118</v>
       </c>
       <c r="N10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1281,7 +1284,7 @@
         <v>118</v>
       </c>
       <c r="N11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1325,7 +1328,7 @@
         <v>118</v>
       </c>
       <c r="N12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1369,7 +1372,7 @@
         <v>118</v>
       </c>
       <c r="N13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1407,7 +1410,7 @@
         <v>56</v>
       </c>
       <c r="L14" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="M14" t="s">
         <v>118</v>
@@ -1457,7 +1460,7 @@
         <v>118</v>
       </c>
       <c r="N15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1501,7 +1504,7 @@
         <v>118</v>
       </c>
       <c r="N16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1545,7 +1548,7 @@
         <v>118</v>
       </c>
       <c r="N17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_24-02-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_24-02-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="141">
   <si>
     <t>SKU</t>
   </si>
@@ -202,9 +202,6 @@
     <t>£40.49</t>
   </si>
   <si>
-    <t>£300</t>
-  </si>
-  <si>
     <t>£18.75</t>
   </si>
   <si>
@@ -395,9 +392,6 @@
   </si>
   <si>
     <t>£59.44</t>
-  </si>
-  <si>
-    <t>£49.00</t>
   </si>
   <si>
     <t>£14.54</t>
@@ -858,37 +852,37 @@
         <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
         <v>56</v>
       </c>
       <c r="H2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K2" t="s">
         <v>56</v>
       </c>
       <c r="L2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -902,37 +896,37 @@
         <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
         <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H3" t="s">
         <v>56</v>
       </c>
       <c r="I3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K3" t="s">
         <v>56</v>
       </c>
       <c r="L3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -946,37 +940,37 @@
         <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
         <v>48</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K4" t="s">
         <v>56</v>
       </c>
       <c r="L4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -990,37 +984,37 @@
         <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
         <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K5" t="s">
         <v>56</v>
       </c>
       <c r="L5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1034,37 +1028,37 @@
         <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>50</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K6" t="s">
         <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1078,37 +1072,37 @@
         <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
         <v>51</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K7" t="s">
         <v>56</v>
       </c>
       <c r="L7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1122,37 +1116,37 @@
         <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>52</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K8" t="s">
         <v>56</v>
       </c>
       <c r="L8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1166,37 +1160,37 @@
         <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E9" t="s">
         <v>53</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s">
         <v>56</v>
       </c>
       <c r="I9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K9" t="s">
         <v>56</v>
       </c>
       <c r="L9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1210,37 +1204,37 @@
         <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
         <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K10" t="s">
         <v>56</v>
       </c>
       <c r="L10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1254,37 +1248,37 @@
         <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
         <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K11" t="s">
         <v>56</v>
       </c>
       <c r="L11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1304,31 +1298,31 @@
         <v>56</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s">
         <v>56</v>
       </c>
       <c r="I12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K12" t="s">
         <v>56</v>
       </c>
       <c r="L12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1342,37 +1336,37 @@
         <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
         <v>57</v>
       </c>
       <c r="F13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K13" t="s">
         <v>56</v>
       </c>
       <c r="L13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1386,7 +1380,7 @@
         <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
         <v>58</v>
@@ -1404,16 +1398,16 @@
         <v>56</v>
       </c>
       <c r="J14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K14" t="s">
         <v>56</v>
       </c>
       <c r="L14" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="M14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N14" t="s">
         <v>56</v>
@@ -1430,37 +1424,37 @@
         <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
         <v>59</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s">
         <v>56</v>
       </c>
       <c r="I15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K15" t="s">
         <v>56</v>
       </c>
       <c r="L15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1474,37 +1468,37 @@
         <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
         <v>60</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s">
         <v>56</v>
       </c>
       <c r="I16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K16" t="s">
         <v>56</v>
       </c>
       <c r="L16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1518,37 +1512,37 @@
         <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s">
         <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K17" t="s">
         <v>56</v>
       </c>
       <c r="L17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
